--- a/djb/benefit_rules.xlsx
+++ b/djb/benefit_rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\R_projects\Reason\gang\Florida-FRS-main_generalizable\djb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F4DA0B-FA51-4D5E-BFD3-8019ED3020B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C6BE8E-BDD7-4B47-9ECD-C6D68D084A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{0527D138-38C7-42E4-8E45-E7785205E030}"/>
   </bookViews>
@@ -403,16 +403,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>7621</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>312421</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>98303</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>114899</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>403103</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>599</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -435,7 +435,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10828021" y="2842260"/>
+          <a:off x="11742421" y="533400"/>
           <a:ext cx="8625082" cy="8976959"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -447,16 +447,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>58380</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>154037</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>12660</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>115937</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -479,7 +479,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10965180" y="571500"/>
+          <a:off x="18844260" y="3093720"/>
           <a:ext cx="5400000" cy="2142857"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/djb/benefit_rules.xlsx
+++ b/djb/benefit_rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\R_projects\Reason\gang\Florida-FRS-main_generalizable\djb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C6BE8E-BDD7-4B47-9ECD-C6D68D084A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D978AB99-285E-439B-9DA3-6CA0D05FD737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{0527D138-38C7-42E4-8E45-E7785205E030}"/>
   </bookViews>
@@ -403,16 +403,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>312421</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>97675</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1386</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>403103</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>188357</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>599</xdr:rowOff>
+      <xdr:rowOff>14454</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -435,8 +435,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11742421" y="533400"/>
-          <a:ext cx="8625082" cy="8976959"/>
+          <a:off x="10911148" y="541713"/>
+          <a:ext cx="8625082" cy="8838414"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -447,16 +447,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>542405</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>77585</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>12660</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>115937</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>456005</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>25883</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -479,8 +479,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18844260" y="3093720"/>
-          <a:ext cx="5400000" cy="2142857"/>
+          <a:off x="16842278" y="2779221"/>
+          <a:ext cx="5400000" cy="2109607"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
